--- a/data/trans_orig/P5707-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5707-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2007</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>323900</t>
+          <t>324569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>376724</t>
+          <t>373581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>287718</t>
+          <t>284411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>340855</t>
+          <t>337536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>623711</t>
+          <t>624759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>697406</t>
+          <t>699087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200066</t>
+          <t>199546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248386</t>
+          <t>249298</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202339</t>
+          <t>200851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249280</t>
+          <t>247175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>414533</t>
+          <t>416772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480805</t>
+          <t>487421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87734</t>
+          <t>87323</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126757</t>
+          <t>127748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96214</t>
+          <t>97534</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136045</t>
+          <t>136225</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>197903</t>
+          <t>199468</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>253261</t>
+          <t>251434</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>23847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44024</t>
+          <t>44657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32556</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60961</t>
+          <t>60382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>521208</t>
+          <t>521970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>583466</t>
+          <t>585947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>523506</t>
+          <t>523746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>587751</t>
+          <t>586740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1064359</t>
+          <t>1062445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1152556</t>
+          <t>1150794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233506</t>
+          <t>232221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288941</t>
+          <t>290323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236439</t>
+          <t>236348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295183</t>
+          <t>291426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>486813</t>
+          <t>485653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>564565</t>
+          <t>563508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98038</t>
+          <t>99592</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141757</t>
+          <t>140035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103762</t>
+          <t>104478</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147725</t>
+          <t>149791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216172</t>
+          <t>216969</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274597</t>
+          <t>277648</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36888</t>
+          <t>35067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,82 +1769,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>20402</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12644</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32423</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>43999</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>31965</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>59875</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,66%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20402</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12394</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31584</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>43999</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>32667</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>59445</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390845</t>
+          <t>390429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>445839</t>
+          <t>444601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>383854</t>
+          <t>387153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>433878</t>
+          <t>435087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>790907</t>
+          <t>792491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>863353</t>
+          <t>864673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152777</t>
+          <t>152431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201284</t>
+          <t>200431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144631</t>
+          <t>143351</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186103</t>
+          <t>186815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309165</t>
+          <t>309185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373444</t>
+          <t>374228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50373</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82020</t>
+          <t>81706</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67295</t>
+          <t>67214</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100488</t>
+          <t>99526</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124039</t>
+          <t>125907</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>168395</t>
+          <t>170440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>38474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>30959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56871</t>
+          <t>56482</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>509465</t>
+          <t>513985</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>570384</t>
+          <t>571033</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>560917</t>
+          <t>559371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>625533</t>
+          <t>621043</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1084842</t>
+          <t>1088134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1173210</t>
+          <t>1171534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233937</t>
+          <t>230489</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230746</t>
+          <t>230450</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>287375</t>
+          <t>285718</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>479770</t>
+          <t>481069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>556800</t>
+          <t>556196</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83301</t>
+          <t>83521</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121112</t>
+          <t>120779</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>105413</t>
+          <t>104675</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>146257</t>
+          <t>145052</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>199338</t>
+          <t>199351</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>256669</t>
+          <t>255011</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27917</t>
+          <t>28146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53741</t>
+          <t>52453</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>40937</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72136</t>
+          <t>71599</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73942</t>
+          <t>74667</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113576</t>
+          <t>113825</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1798989</t>
+          <t>1797343</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1913151</t>
+          <t>1911884</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1812354</t>
+          <t>1808213</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1930201</t>
+          <t>1924366</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3648158</t>
+          <t>3644789</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3813011</t>
+          <t>3805966</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>870477</t>
+          <t>868778</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>976071</t>
+          <t>969670</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>857747</t>
+          <t>858341</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>960037</t>
+          <t>961824</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1761809</t>
+          <t>1759734</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1902616</t>
+          <t>1906674</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>357350</t>
+          <t>353530</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>429758</t>
+          <t>428646</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>410226</t>
+          <t>407229</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>489659</t>
+          <t>488282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>785062</t>
+          <t>783576</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>893801</t>
+          <t>887976</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73200</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>113537</t>
+          <t>110334</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>111511</t>
+          <t>111553</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>159849</t>
+          <t>157598</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>192374</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>255986</t>
+          <t>258191</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26084</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>44488</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2012</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>430065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>479856</t>
+          <t>481229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>399900</t>
+          <t>400861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>451960</t>
+          <t>454109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>843938</t>
+          <t>844949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>916987</t>
+          <t>915266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164585</t>
+          <t>163357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213711</t>
+          <t>210844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178841</t>
+          <t>180113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229451</t>
+          <t>230216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>360130</t>
+          <t>356634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>427510</t>
+          <t>424647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31018</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56817</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28984</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>55588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67880</t>
+          <t>68587</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104183</t>
+          <t>104516</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>21709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29046</t>
+          <t>26606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43758</t>
+          <t>44030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>575057</t>
+          <t>574298</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>640549</t>
+          <t>641192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>570743</t>
+          <t>572124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>633623</t>
+          <t>636978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1168890</t>
+          <t>1163807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1256751</t>
+          <t>1255198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239266</t>
+          <t>238971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299425</t>
+          <t>298690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276198</t>
+          <t>275514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337116</t>
+          <t>336232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534086</t>
+          <t>533686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>615808</t>
+          <t>617217</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86927</t>
+          <t>86759</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125985</t>
+          <t>127488</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75123</t>
+          <t>75168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>112876</t>
+          <t>113398</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>173894</t>
+          <t>171924</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>229772</t>
+          <t>227482</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40294</t>
+          <t>41914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33520</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,47 +5446,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>49333</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>35634</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>66497</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>3,25%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>49333</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>35386</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>65775</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>447181</t>
+          <t>446347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>504112</t>
+          <t>504858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>443634</t>
+          <t>441614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>501404</t>
+          <t>498127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>904274</t>
+          <t>908180</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>987460</t>
+          <t>987647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150221</t>
+          <t>152567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198490</t>
+          <t>199505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173480</t>
+          <t>174072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226019</t>
+          <t>225845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335590</t>
+          <t>339004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413378</t>
+          <t>409920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67546</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105426</t>
+          <t>107141</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63773</t>
+          <t>65685</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101697</t>
+          <t>101928</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>143697</t>
+          <t>143851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>196444</t>
+          <t>196451</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,47 +6128,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>30935</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>20953</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>44820</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>30935</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>20367</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>43237</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>23233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>510739</t>
+          <t>509466</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571254</t>
+          <t>571914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>546639</t>
+          <t>547528</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>610692</t>
+          <t>610258</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1074152</t>
+          <t>1076709</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1162930</t>
+          <t>1167493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,51%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233735</t>
+          <t>229190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>286228</t>
+          <t>288947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277503</t>
+          <t>278039</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>335736</t>
+          <t>335233</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>524359</t>
+          <t>521194</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>608257</t>
+          <t>603791</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100775</t>
+          <t>99700</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144961</t>
+          <t>143779</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>111433</t>
+          <t>109922</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154167</t>
+          <t>155249</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>222105</t>
+          <t>223221</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>282105</t>
+          <t>286094</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33127</t>
+          <t>32236</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29429</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>30278</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55576</t>
+          <t>56332</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>27984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2017960</t>
+          <t>2015535</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2142333</t>
+          <t>2132516</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2018828</t>
+          <t>2024658</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2142286</t>
+          <t>2145324</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4075620</t>
+          <t>4075111</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4256490</t>
+          <t>4244810</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>835071</t>
+          <t>837266</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>941189</t>
+          <t>947806</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>960113</t>
+          <t>953436</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1070006</t>
+          <t>1070195</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1821908</t>
+          <t>1825163</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1976943</t>
+          <t>1982372</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>322704</t>
+          <t>321296</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>399054</t>
+          <t>393096</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>308184</t>
+          <t>312651</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>380408</t>
+          <t>382803</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>651149</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>759966</t>
+          <t>756951</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58083</t>
+          <t>56826</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>93206</t>
+          <t>92659</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>61092</t>
+          <t>61005</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>99572</t>
+          <t>98287</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>129279</t>
+          <t>128184</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>178796</t>
+          <t>179983</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>29876</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7575,42 +7575,42 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>31631</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>45718</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>31631</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>21581</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>46769</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>36851</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>66454</t>
+          <t>67849</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2016</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>290353</t>
+          <t>290599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>343520</t>
+          <t>342212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>290103</t>
+          <t>291298</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>340175</t>
+          <t>344457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>593671</t>
+          <t>595066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>666550</t>
+          <t>668233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214986</t>
+          <t>217615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265280</t>
+          <t>266553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221264</t>
+          <t>221269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271770</t>
+          <t>270780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>452950</t>
+          <t>453585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>523757</t>
+          <t>524135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75893</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112459</t>
+          <t>111358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71852</t>
+          <t>71989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107611</t>
+          <t>107885</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>159917</t>
+          <t>158770</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>208774</t>
+          <t>205920</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28728</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51894</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>493946</t>
+          <t>497471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>558738</t>
+          <t>563282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>517232</t>
+          <t>517231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>584622</t>
+          <t>581789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1033321</t>
+          <t>1029639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1126181</t>
+          <t>1128466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296697</t>
+          <t>294567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>359513</t>
+          <t>357689</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317423</t>
+          <t>318561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381567</t>
+          <t>381921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634203</t>
+          <t>628043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>719528</t>
+          <t>718093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119069</t>
+          <t>119364</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164656</t>
+          <t>164624</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99575</t>
+          <t>99238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142054</t>
+          <t>139721</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>229182</t>
+          <t>231327</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>291876</t>
+          <t>295466</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>30896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28362</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50297</t>
+          <t>49835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>291092</t>
+          <t>290513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>348270</t>
+          <t>346548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>360840</t>
+          <t>358403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>610950</t>
+          <t>613107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>690289</t>
+          <t>693015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258233</t>
+          <t>258750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>313680</t>
+          <t>316043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>266292</t>
+          <t>266077</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>320078</t>
+          <t>319315</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>540988</t>
+          <t>539492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>619113</t>
+          <t>616568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119363</t>
+          <t>118887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163416</t>
+          <t>163803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>116329</t>
+          <t>113935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157370</t>
+          <t>159073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>244201</t>
+          <t>245075</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>306496</t>
+          <t>310403</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19381</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>486816</t>
+          <t>485027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>547796</t>
+          <t>545284</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>548818</t>
+          <t>555880</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>617711</t>
+          <t>623982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1051301</t>
+          <t>1059851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1146691</t>
+          <t>1148141</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245404</t>
+          <t>244716</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>302432</t>
+          <t>301910</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>263651</t>
+          <t>259876</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>325999</t>
+          <t>320861</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>525029</t>
+          <t>524106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>607856</t>
+          <t>607029</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103406</t>
+          <t>101643</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144825</t>
+          <t>143748</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99776</t>
+          <t>100106</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>142469</t>
+          <t>141848</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>211517</t>
+          <t>213390</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>273793</t>
+          <t>271850</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>25110</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25384</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49879</t>
+          <t>51555</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>39470</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70178</t>
+          <t>68044</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>26482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1621395</t>
+          <t>1619448</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1738120</t>
+          <t>1740814</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1721424</t>
+          <t>1725354</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1840070</t>
+          <t>1844609</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3374702</t>
+          <t>3373807</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3556692</t>
+          <t>3548486</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1066733</t>
+          <t>1075061</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1180448</t>
+          <t>1188310</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1122714</t>
+          <t>1123286</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1237431</t>
+          <t>1240930</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2228336</t>
+          <t>2230772</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2385954</t>
+          <t>2389522</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>455400</t>
+          <t>454285</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>541430</t>
+          <t>540372</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>428514</t>
+          <t>424347</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>510986</t>
+          <t>512410</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>896356</t>
+          <t>907040</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1015022</t>
+          <t>1024004</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>53153</t>
+          <t>53167</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>86436</t>
+          <t>86205</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>70570</t>
+          <t>68576</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>108531</t>
+          <t>107613</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>128749</t>
+          <t>130887</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>182203</t>
+          <t>181620</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,47 +11212,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>20241</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>12625</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>31941</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>20241</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>12160</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>31566</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>28171</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2023</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>351054</t>
+          <t>350079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>402541</t>
+          <t>403805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>354225</t>
+          <t>356320</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>394946</t>
+          <t>394484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>717541</t>
+          <t>717674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>786558</t>
+          <t>783825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161380</t>
+          <t>157865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>207490</t>
+          <t>203984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180112</t>
+          <t>179259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216109</t>
+          <t>214773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350371</t>
+          <t>350052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>409525</t>
+          <t>409600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38786</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65976</t>
+          <t>65668</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,82 +11900,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>66153</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>55052</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>77158</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>116839</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>101889</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>136283</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>10,44%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>66153</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>55378</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>78847</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>116839</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>100168</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>136836</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>22785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36023</t>
+          <t>35888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32360</t>
+          <t>32514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53455</t>
+          <t>54190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22699</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>624700</t>
+          <t>624268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>937474</t>
+          <t>972440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>479646</t>
+          <t>478841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>533312</t>
+          <t>531566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1134857</t>
+          <t>1130971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1562518</t>
+          <t>1562200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191130</t>
+          <t>164224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430220</t>
+          <t>429897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305387</t>
+          <t>307965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>354856</t>
+          <t>355251</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>432053</t>
+          <t>435498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>757167</t>
+          <t>757836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36653</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101089</t>
+          <t>102486</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63825</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91832</t>
+          <t>92518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99073</t>
+          <t>105980</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179364</t>
+          <t>180119</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>42288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24769</t>
+          <t>24457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75423</t>
+          <t>75416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31989</t>
+          <t>32741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>347947</t>
+          <t>348381</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>409672</t>
+          <t>409604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187816</t>
+          <t>207339</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>544655</t>
+          <t>544210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>494257</t>
+          <t>490322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>922665</t>
+          <t>925730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,61%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>223220</t>
+          <t>225790</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282584</t>
+          <t>285342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116679</t>
+          <t>131000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>321731</t>
+          <t>324219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309091</t>
+          <t>308340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>588021</t>
+          <t>583106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>42220</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75076</t>
+          <t>75936</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>73054</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70840</t>
+          <t>69647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135329</t>
+          <t>133887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19369</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>591869</t>
+          <t>559828</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>773803</t>
+          <t>767223</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,47 +13525,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>7527</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>3407</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>13742</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>7527</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>3515</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>13887</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>527365</t>
+          <t>532128</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>590573</t>
+          <t>593761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>661005</t>
+          <t>660981</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>779046</t>
+          <t>776299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1212681</t>
+          <t>1213530</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1342311</t>
+          <t>1343971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235484</t>
+          <t>235672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>292682</t>
+          <t>288248</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>224557</t>
+          <t>222732</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311401</t>
+          <t>312562</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>476139</t>
+          <t>479203</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>585147</t>
+          <t>582866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48944</t>
+          <t>47703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78133</t>
+          <t>75020</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>49538</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78323</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>104359</t>
+          <t>106483</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>146291</t>
+          <t>147096</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47806</t>
+          <t>47266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43913</t>
+          <t>43741</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51665</t>
+          <t>50283</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84214</t>
+          <t>82897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1944589</t>
+          <t>1947052</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2380806</t>
+          <t>2392570</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1598701</t>
+          <t>1647238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2145822</t>
+          <t>2148635</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3708488</t>
+          <t>3737633</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4369089</t>
+          <t>4362403</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>795705</t>
+          <t>795132</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1126102</t>
+          <t>1128983</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>865369</t>
+          <t>849653</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1144003</t>
+          <t>1141930</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1827115</t>
+          <t>1768482</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2238763</t>
+          <t>2221566</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>191471</t>
+          <t>188799</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>283236</t>
+          <t>280935</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>209752</t>
+          <t>212348</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>290633</t>
+          <t>290463</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>436583</t>
+          <t>435554</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>551575</t>
+          <t>553837</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>64444</t>
+          <t>64077</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>108461</t>
+          <t>107633</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>107027</t>
+          <t>106707</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>932666</t>
+          <t>939247</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>186084</t>
+          <t>187187</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1234264</t>
+          <t>1184423</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27036</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49746</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>49552</t>
+          <t>50055</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>80955</t>
+          <t>79320</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5707-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5707-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>324569</t>
+          <t>321138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>373581</t>
+          <t>374198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>284411</t>
+          <t>286938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>337536</t>
+          <t>335891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>624759</t>
+          <t>621467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>699087</t>
+          <t>696026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199546</t>
+          <t>199136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249298</t>
+          <t>250232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>200595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247175</t>
+          <t>248263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>416772</t>
+          <t>414962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>487421</t>
+          <t>482593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87323</t>
+          <t>90054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127748</t>
+          <t>127226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97534</t>
+          <t>98424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136225</t>
+          <t>136314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>199468</t>
+          <t>196610</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251434</t>
+          <t>252336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23847</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>43920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>33395</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60382</t>
+          <t>62708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>521970</t>
+          <t>521024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>585947</t>
+          <t>584588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>523746</t>
+          <t>525153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>586740</t>
+          <t>587545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1062445</t>
+          <t>1061789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1150794</t>
+          <t>1151600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232221</t>
+          <t>229751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290323</t>
+          <t>289461</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236348</t>
+          <t>236602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291426</t>
+          <t>292199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>485653</t>
+          <t>488938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>563508</t>
+          <t>566279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99592</t>
+          <t>100994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>140035</t>
+          <t>141285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104478</t>
+          <t>105407</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149791</t>
+          <t>147645</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216969</t>
+          <t>216274</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>277648</t>
+          <t>276670</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35067</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>30846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59875</t>
+          <t>58991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390429</t>
+          <t>392017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>444601</t>
+          <t>441693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>387153</t>
+          <t>384815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>435087</t>
+          <t>434722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>792491</t>
+          <t>788991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>864673</t>
+          <t>862747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152431</t>
+          <t>155654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200431</t>
+          <t>200257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143351</t>
+          <t>142558</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186815</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309185</t>
+          <t>307300</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374228</t>
+          <t>375734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50040</t>
+          <t>50838</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81706</t>
+          <t>82186</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67214</t>
+          <t>66239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99526</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125907</t>
+          <t>123921</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>170440</t>
+          <t>170987</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30959</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>56724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14056</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>513985</t>
+          <t>509689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571033</t>
+          <t>569728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>559371</t>
+          <t>558148</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>621043</t>
+          <t>621943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1088134</t>
+          <t>1086654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1171534</t>
+          <t>1175597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230489</t>
+          <t>231686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>285292</t>
+          <t>285067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230450</t>
+          <t>232468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285718</t>
+          <t>287013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>481069</t>
+          <t>476748</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>556196</t>
+          <t>554003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83521</t>
+          <t>84679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120779</t>
+          <t>121588</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>104675</t>
+          <t>104689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>145052</t>
+          <t>149111</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>199351</t>
+          <t>198962</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>255011</t>
+          <t>256668</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28146</t>
+          <t>27179</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52453</t>
+          <t>52777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>41147</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71599</t>
+          <t>71948</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74667</t>
+          <t>75209</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113825</t>
+          <t>113921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20412</t>
+          <t>21191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1797343</t>
+          <t>1800972</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1911884</t>
+          <t>1914104</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1808213</t>
+          <t>1810851</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1924366</t>
+          <t>1927791</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3644789</t>
+          <t>3648416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3805966</t>
+          <t>3807834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>868778</t>
+          <t>871347</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>969670</t>
+          <t>979352</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>858341</t>
+          <t>859524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>961824</t>
+          <t>964998</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1759734</t>
+          <t>1750587</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1906674</t>
+          <t>1895368</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>353530</t>
+          <t>355661</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>428646</t>
+          <t>428934</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>407229</t>
+          <t>409883</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>488282</t>
+          <t>490619</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>783576</t>
+          <t>788210</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>887976</t>
+          <t>899801</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>72364</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>110334</t>
+          <t>110628</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>111553</t>
+          <t>112316</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>157598</t>
+          <t>157358</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>196243</t>
+          <t>198659</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>258191</t>
+          <t>259014</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25466</t>
+          <t>26369</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25999</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>44488</t>
+          <t>45742</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>430065</t>
+          <t>425141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>481229</t>
+          <t>477232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,47 +4390,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>60,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>426763</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>401176</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>451499</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>61,22%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>426763</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>400861</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>454109</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>61,22%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>844949</t>
+          <t>842097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>915266</t>
+          <t>916267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163357</t>
+          <t>162626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>210844</t>
+          <t>212646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180113</t>
+          <t>181226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230216</t>
+          <t>231717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>356634</t>
+          <t>358962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>424647</t>
+          <t>426566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>31497</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57060</t>
+          <t>57654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>30309</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55588</t>
+          <t>57418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>67049</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104516</t>
+          <t>103906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>21975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21078</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44030</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12613</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>20431</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>574298</t>
+          <t>575251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>641192</t>
+          <t>644824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>572124</t>
+          <t>570664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>636978</t>
+          <t>638265</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1163807</t>
+          <t>1164189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1255198</t>
+          <t>1254171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238971</t>
+          <t>238153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298690</t>
+          <t>300270</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275514</t>
+          <t>276517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336232</t>
+          <t>337905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>533686</t>
+          <t>536813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>617217</t>
+          <t>622707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>87126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127488</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75168</t>
+          <t>75505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113398</t>
+          <t>112586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>171924</t>
+          <t>173052</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227482</t>
+          <t>228426</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41914</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32365</t>
+          <t>33857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35634</t>
+          <t>36938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66497</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>446347</t>
+          <t>447032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>504858</t>
+          <t>505593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>441614</t>
+          <t>444050</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>498127</t>
+          <t>501042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>908180</t>
+          <t>909927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>987647</t>
+          <t>986258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,44%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152567</t>
+          <t>149172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199505</t>
+          <t>198210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174072</t>
+          <t>173366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>225845</t>
+          <t>224215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339004</t>
+          <t>338846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409920</t>
+          <t>407455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69527</t>
+          <t>67216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107141</t>
+          <t>105951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65685</t>
+          <t>65132</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101928</t>
+          <t>100348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>143851</t>
+          <t>143440</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>197232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20635</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>29757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44820</t>
+          <t>44407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>509466</t>
+          <t>510762</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571914</t>
+          <t>572043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>547528</t>
+          <t>546323</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>610258</t>
+          <t>610920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1076709</t>
+          <t>1076357</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1167493</t>
+          <t>1162545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229190</t>
+          <t>233236</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288947</t>
+          <t>286938</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278039</t>
+          <t>274536</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>335233</t>
+          <t>333951</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>521194</t>
+          <t>523209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>603791</t>
+          <t>604954</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99700</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143779</t>
+          <t>145583</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>109922</t>
+          <t>111295</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155249</t>
+          <t>153647</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>223221</t>
+          <t>223511</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>286094</t>
+          <t>284062</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32236</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30774</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56332</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,42 +6893,42 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>14538</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>8472</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>25224</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>14538</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>8067</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>24886</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27984</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2015535</t>
+          <t>2017555</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2132516</t>
+          <t>2141269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2024658</t>
+          <t>2027397</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2145324</t>
+          <t>2142927</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4075111</t>
+          <t>4072870</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4244810</t>
+          <t>4245799</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>837266</t>
+          <t>833872</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>947806</t>
+          <t>940602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>953436</t>
+          <t>959411</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1070195</t>
+          <t>1068065</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1825163</t>
+          <t>1814795</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1982372</t>
+          <t>1975135</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>321296</t>
+          <t>319422</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>393096</t>
+          <t>396923</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>312651</t>
+          <t>314943</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>382803</t>
+          <t>387110</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>651149</t>
+          <t>647075</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>756951</t>
+          <t>753489</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56826</t>
+          <t>57806</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>92659</t>
+          <t>94042</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>61005</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98287</t>
+          <t>97264</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>128184</t>
+          <t>128291</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>179983</t>
+          <t>180107</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29876</t>
+          <t>30081</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>47066</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>36851</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>67849</t>
+          <t>67666</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>290599</t>
+          <t>289486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>342212</t>
+          <t>341516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,47 +8032,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>315902</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>289374</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>341477</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>47,09%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>43,13%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>315902</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>291298</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>344457</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>595066</t>
+          <t>593561</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>668233</t>
+          <t>665460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>217615</t>
+          <t>216556</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266553</t>
+          <t>264357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221269</t>
+          <t>221725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270780</t>
+          <t>268426</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>453585</t>
+          <t>454397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>524135</t>
+          <t>529845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75672</t>
+          <t>76616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111358</t>
+          <t>113696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71989</t>
+          <t>72461</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107885</t>
+          <t>107914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158770</t>
+          <t>156560</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>205920</t>
+          <t>208243</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32347</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51484</t>
+          <t>51437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>497471</t>
+          <t>495666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>563282</t>
+          <t>562024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>517231</t>
+          <t>516275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>581789</t>
+          <t>583840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1029639</t>
+          <t>1031140</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1128466</t>
+          <t>1121182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294567</t>
+          <t>294748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>357689</t>
+          <t>356325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318561</t>
+          <t>318210</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381921</t>
+          <t>381330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628043</t>
+          <t>631462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>718093</t>
+          <t>720271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119364</t>
+          <t>119647</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164624</t>
+          <t>165277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>99154</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>139721</t>
+          <t>141836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>231327</t>
+          <t>227213</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>295466</t>
+          <t>291345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30896</t>
+          <t>30948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>25498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49835</t>
+          <t>51572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>21706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>290513</t>
+          <t>290128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>346548</t>
+          <t>347081</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303441</t>
+          <t>304880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>358403</t>
+          <t>359616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>613107</t>
+          <t>610696</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>693015</t>
+          <t>688789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258750</t>
+          <t>257469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>316043</t>
+          <t>312633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>266077</t>
+          <t>263624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319315</t>
+          <t>318436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>539492</t>
+          <t>536940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>616568</t>
+          <t>617333</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118887</t>
+          <t>120011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163803</t>
+          <t>165270</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113935</t>
+          <t>115074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159073</t>
+          <t>159144</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>245075</t>
+          <t>245714</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>310403</t>
+          <t>308852</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26184</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38341</t>
+          <t>39050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>485027</t>
+          <t>485256</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>545284</t>
+          <t>547241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>555880</t>
+          <t>553027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>623982</t>
+          <t>619173</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1059851</t>
+          <t>1057986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1148141</t>
+          <t>1148788</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,05%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>244716</t>
+          <t>245329</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>301910</t>
+          <t>301350</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>259876</t>
+          <t>264951</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320861</t>
+          <t>325833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>524106</t>
+          <t>523931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>607029</t>
+          <t>604102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>101643</t>
+          <t>102380</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143748</t>
+          <t>143030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,82 +10304,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>120875</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>101132</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>144492</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>242504</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>215134</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>273125</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>12,25%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>10,87%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>120875</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>100106</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>141848</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>242504</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>213390</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>271850</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>25231</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25276</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51555</t>
+          <t>51308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>39792</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>69855</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26482</t>
+          <t>24551</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1619448</t>
+          <t>1619571</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1740814</t>
+          <t>1735962</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1725354</t>
+          <t>1722163</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1844609</t>
+          <t>1842237</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3373807</t>
+          <t>3384413</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3548486</t>
+          <t>3552739</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1075061</t>
+          <t>1072513</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1188310</t>
+          <t>1183060</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1123286</t>
+          <t>1121335</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1240930</t>
+          <t>1237614</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2230772</t>
+          <t>2225615</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2389522</t>
+          <t>2376017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>454285</t>
+          <t>458000</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>540372</t>
+          <t>538082</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>424347</t>
+          <t>422589</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>512410</t>
+          <t>503473</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>907040</t>
+          <t>902074</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1024004</t>
+          <t>1018471</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>53167</t>
+          <t>52471</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>86205</t>
+          <t>87318</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>68576</t>
+          <t>69700</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>107613</t>
+          <t>109272</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>130887</t>
+          <t>129928</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>181620</t>
+          <t>182034</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,49 +11212,49 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>20241</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>12705</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>31839</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>20241</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>12625</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>31941</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>37</t>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>29376</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>55732</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>378191</t>
+          <t>400093</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>350079</t>
+          <t>371330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>403805</t>
+          <t>428038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>374642</t>
+          <t>403416</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>356320</t>
+          <t>379508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>394484</t>
+          <t>424574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>752833</t>
+          <t>803509</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>717674</t>
+          <t>768342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>783825</t>
+          <t>840522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>180966</t>
+          <t>201085</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157865</t>
+          <t>177032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203984</t>
+          <t>227830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>197318</t>
+          <t>217213</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179259</t>
+          <t>198323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214773</t>
+          <t>238438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>378284</t>
+          <t>418298</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350052</t>
+          <t>388499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>409600</t>
+          <t>450007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50687</t>
+          <t>59907</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40813</t>
+          <t>47200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65668</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66153</t>
+          <t>70585</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55052</t>
+          <t>58759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77158</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116839</t>
+          <t>130493</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>101889</t>
+          <t>112171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136283</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>29638</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20799</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35888</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,22 +12063,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41614</t>
+          <t>45605</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32514</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54190</t>
+          <t>58765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>29173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>632149</t>
+          <t>687214</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>632149</t>
+          <t>687214</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>632149</t>
+          <t>687214</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>673107</t>
+          <t>730334</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>673107</t>
+          <t>730334</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>673107</t>
+          <t>730334</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1305256</t>
+          <t>1417548</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1305256</t>
+          <t>1417548</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1305256</t>
+          <t>1417548</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>752407</t>
+          <t>548336</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>624268</t>
+          <t>510904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>972440</t>
+          <t>583352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>506798</t>
+          <t>557531</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>478841</t>
+          <t>528263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>531566</t>
+          <t>587657</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1259205</t>
+          <t>1105868</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1130971</t>
+          <t>1057090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1562200</t>
+          <t>1151021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>330651</t>
+          <t>369487</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>334334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429897</t>
+          <t>404559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>328906</t>
+          <t>374393</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307965</t>
+          <t>344863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>355251</t>
+          <t>401561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>659557</t>
+          <t>743880</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>435498</t>
+          <t>699888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>757836</t>
+          <t>791802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74698</t>
+          <t>85264</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>68882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102486</t>
+          <t>106176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76728</t>
+          <t>85319</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64808</t>
+          <t>71906</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92518</t>
+          <t>100875</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>151426</t>
+          <t>170583</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105980</t>
+          <t>148777</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>180119</t>
+          <t>197529</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>32866</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42288</t>
+          <t>47927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31867</t>
+          <t>38322</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>48195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58822</t>
+          <t>71188</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75416</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,17 +12823,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24577</t>
+          <t>25145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>15637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32741</t>
+          <t>38890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192018</t>
+          <t>1046313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192018</t>
+          <t>1046313</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192018</t>
+          <t>1046313</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956293</t>
+          <t>1068878</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956293</t>
+          <t>1068878</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956293</t>
+          <t>1068878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2148312</t>
+          <t>2115192</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2148312</t>
+          <t>2115192</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2148312</t>
+          <t>2115192</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>380113</t>
+          <t>421441</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>348381</t>
+          <t>387143</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>409604</t>
+          <t>454556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>413676</t>
+          <t>447745</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>207339</t>
+          <t>422216</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>544210</t>
+          <t>473278</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,27 +13088,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>793788</t>
+          <t>869186</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>490322</t>
+          <t>824815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>925730</t>
+          <t>911988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>253299</t>
+          <t>294361</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>225790</t>
+          <t>259533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285342</t>
+          <t>326567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>242859</t>
+          <t>277666</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131000</t>
+          <t>253206</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>324219</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>496158</t>
+          <t>572028</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308340</t>
+          <t>534451</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>583106</t>
+          <t>613383</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>66686</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>50346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75936</t>
+          <t>92220</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50669</t>
+          <t>61734</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>48180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73054</t>
+          <t>77430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>106886</t>
+          <t>128419</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>107190</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133887</t>
+          <t>153377</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>218894</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>559828</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>230854</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>767223</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -13470,22 +13470,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>931303</t>
+          <t>809664</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>931303</t>
+          <t>809664</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>931303</t>
+          <t>809664</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1635214</t>
+          <t>1610865</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1635214</t>
+          <t>1610865</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1635214</t>
+          <t>1610865</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>562130</t>
+          <t>589968</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>532128</t>
+          <t>557206</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>593761</t>
+          <t>622053</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>699287</t>
+          <t>673516</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>660981</t>
+          <t>644777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>776299</t>
+          <t>702638</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1261416</t>
+          <t>1263484</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1213530</t>
+          <t>1219166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1343971</t>
+          <t>1305890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>261862</t>
+          <t>279432</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235672</t>
+          <t>250123</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288248</t>
+          <t>307427</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>280967</t>
+          <t>309818</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222732</t>
+          <t>281217</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>312562</t>
+          <t>337175</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>542829</t>
+          <t>589250</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>479203</t>
+          <t>553599</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>582866</t>
+          <t>632822</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>61372</t>
+          <t>73180</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47703</t>
+          <t>58497</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>75020</t>
+          <t>91535</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>64725</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49538</t>
+          <t>62381</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>79072</t>
+          <t>91884</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>126098</t>
+          <t>148597</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>106483</t>
+          <t>127513</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147096</t>
+          <t>171729</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>35547</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22770</t>
+          <t>25129</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>51627</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33072</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>30840</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43741</t>
+          <t>51452</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>64871</t>
+          <t>75540</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50283</t>
+          <t>60968</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82897</t>
+          <t>92369</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>23742</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>18546</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>36442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>924558</t>
+          <t>987918</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>924558</t>
+          <t>987918</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>924558</t>
+          <t>987918</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1091088</t>
+          <t>1115069</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1091088</t>
+          <t>1115069</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1091088</t>
+          <t>1115069</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2015646</t>
+          <t>2102987</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2015646</t>
+          <t>2102987</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2015646</t>
+          <t>2102987</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2072840</t>
+          <t>1959838</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1947052</t>
+          <t>1895020</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2392570</t>
+          <t>2028794</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1994403</t>
+          <t>2082210</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1647238</t>
+          <t>2027430</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2148635</t>
+          <t>2134476</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4067243</t>
+          <t>4042048</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3737633</t>
+          <t>3947730</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4362403</t>
+          <t>4121926</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1026779</t>
+          <t>1144365</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>795132</t>
+          <t>1079432</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1128983</t>
+          <t>1201963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1050049</t>
+          <t>1179090</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>849653</t>
+          <t>1130346</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1141930</t>
+          <t>1229552</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2076828</t>
+          <t>2323455</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1768482</t>
+          <t>2245004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2221566</t>
+          <t>2405107</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>242974</t>
+          <t>285037</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>188799</t>
+          <t>252885</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>280935</t>
+          <t>318836</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>258275</t>
+          <t>293055</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>212348</t>
+          <t>266353</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>290463</t>
+          <t>319445</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>501249</t>
+          <t>578092</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>435554</t>
+          <t>535080</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>553837</t>
+          <t>623191</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>84747</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>64077</t>
+          <t>80597</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>107633</t>
+          <t>123406</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>311414</t>
+          <t>124418</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>106707</t>
+          <t>107615</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>939247</t>
+          <t>143634</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>396161</t>
+          <t>224819</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>187187</t>
+          <t>201148</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1184423</t>
+          <t>255155</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>46094</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>37650</t>
+          <t>45174</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>60215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>62947</t>
+          <t>78179</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50055</t>
+          <t>63651</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>79320</t>
+          <t>96910</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3452637</t>
+          <t>3522646</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3452637</t>
+          <t>3522646</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3452637</t>
+          <t>3522646</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3651791</t>
+          <t>3723946</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3651791</t>
+          <t>3723946</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3651791</t>
+          <t>3723946</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7104428</t>
+          <t>7246592</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7104428</t>
+          <t>7246592</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7104428</t>
+          <t>7246592</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
